--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>28-Jul 18:35</t>
+          <t>28-Jul 19:32</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹105 (24.71%) 60 ↓ / 105 ↑</t>
+          <t>₹106 (24.94%) 60 ↓ / 106 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>28-Jul 19:32</t>
+          <t>29-Jul 11:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,61 +486,124 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Ardee Industries IPOU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹13 (24.53%) 13 ↓ / 13 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>53</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹425.87 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>281</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>5-Aug</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7-Aug</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>10-Aug</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>12-Aug</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>29-Jul 16:33</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>MV Electrosystems IPOU</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>₹106 (24.94%) 60 ↓ / 106 ↑</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>425</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>₹290.00 Cr</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G3" t="n">
         <v>34</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>30-Jul</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>3-Aug</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>4-Aug</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>6-Aug</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>29-Jul 11:00</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>29-Jul 16:30</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>29-Jul 16:33</t>
+          <t>30-Jul 10:59</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -549,12 +549,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOU</t>
+          <t>MV Electrosystems IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹106 (24.94%) 60 ↓ / 106 ↑</t>
+          <t>₹100 (23.53%) 60 ↓ / 106 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4x</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>30-Jul GMP: 100</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>29-Jul 16:30</t>
+          <t>30-Jul 10:57</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOU</t>
+          <t>MV Electrosystems IPOO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹13 (24.53%) 13 ↓ / 13 ↑</t>
+          <t>₹116 (27.29%) 60 ↓ / 116 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,109 +501,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.78x</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹290.00 Cr</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>281</v>
+        <v>34</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>30-Jul GMP: 116</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>30-Jul 10:59</t>
+          <t>30-Jul 16:35</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MV Electrosystems IPOO</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹100 (23.53%) 60 ↓ / 106 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>4x</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>425</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹290.00 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>34</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>30-Jul GMP: 100</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3-Aug</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>4-Aug</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>6-Aug</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>30-Jul 10:57</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹116 (27.29%) 60 ↓ / 116 ↑</t>
+          <t>₹120 (28.24%) 60 ↓ / 120 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.78x</t>
+          <t>3.87x</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -517,7 +517,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 116</t>
+          <t>30-Jul GMP: 120</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>30-Jul 16:35</t>
+          <t>30-Jul 18:53</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,61 +486,124 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Ardee Industries IPOU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹13 (24.53%) 13 ↓ / 13 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>53</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹425.87 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>281</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>5-Aug</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7-Aug</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>10-Aug</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>12-Aug</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>31-Jul 11:34</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>MV Electrosystems IPOO</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>₹120 (28.24%) 60 ↓ / 120 ↑</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹133 (31.29%) 60 ↓ / 133 ↑</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>3.87x</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6.77x</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>425</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>₹290.00 Cr</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G3" t="n">
         <v>34</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>30-Jul GMP: 120</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>30-Jul GMP: 125</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>3-Aug</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>4-Aug</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>6-Aug</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>30-Jul 18:53</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>31-Jul 11:28</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOU</t>
+          <t>MV Electrosystems IPOO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹13 (24.53%) 13 ↓ / 13 ↑</t>
+          <t>₹133 (31.29%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,109 +501,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12.22x</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹290.00 Cr</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>281</v>
+        <v>34</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>30-Jul GMP: 125</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>31-Jul 11:34</t>
+          <t>31-Jul 16:29</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MV Electrosystems IPOO</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹133 (31.29%) 60 ↓ / 133 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>6.77x</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>425</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹290.00 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>34</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>30-Jul GMP: 125</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3-Aug</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>4-Aug</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>6-Aug</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>31-Jul 11:28</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12.22x</t>
+          <t>12.79x</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>31-Jul 16:29</t>
+          <t>1-Aug 10:28</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹133 (31.29%) 60 ↓ / 133 ↑</t>
+          <t>₹115 (27.06%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1-Aug 10:28</t>
+          <t>1-Aug 15:56</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹115 (27.06%) 60 ↓ / 133 ↑</t>
+          <t>₹110 (25.88%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1-Aug 15:56</t>
+          <t>2-Aug 11:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹110 (25.88%) 60 ↓ / 133 ↑</t>
+          <t>₹113 (26.59%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2-Aug 11:00</t>
+          <t>2-Aug 15:55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOO</t>
+          <t>MV Electrosystems IPOCT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹113 (26.59%) 60 ↓ / 133 ↑</t>
+          <t>₹112 (26.35%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12.79x</t>
+          <t>71.07x</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -522,7 +522,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>3-Aug GMP: 112</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2-Aug 15:55</t>
+          <t>3-Aug 11:59</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹112 (26.35%) 60 ↓ / 133 ↑</t>
+          <t>₹100 (23.53%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>71.07x</t>
+          <t>200.66x</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -522,7 +522,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 112</t>
+          <t>3-Aug GMP: 100</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3-Aug 11:59</t>
+          <t>3-Aug 17:30</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOCT</t>
+          <t>Dhoot Transmission IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹100 (23.53%) 60 ↓ / 133 ↑</t>
+          <t>₹200 (22.96%) 146 ↓ / 200 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,43 +501,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>200.66x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>425</v>
+        <v>871</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹290.00 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 125</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 100</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3-Aug 17:30</t>
+          <t>4-Aug 10:57</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹200 (22.96%) 146 ↓ / 200 ↑</t>
+          <t>₹246 (28.24%) 146 ↓ / 246 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4-Aug 10:57</t>
+          <t>4-Aug 16:31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹246 (28.24%) 146 ↓ / 246 ↑</t>
+          <t>₹253 (29.05%) 146 ↓ / 253 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4-Aug 16:31</t>
+          <t>5-Aug 11:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹253 (29.05%) 146 ↓ / 253 ↑</t>
+          <t>₹255 (29.28%) 146 ↓ / 255 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,10 +537,73 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5-Aug 11:00</t>
+          <t>5-Aug 16:31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ardee Industries IPOO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹14 (26.42%) 6.50 ↓ / 14 ↑</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3.03x</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>53</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹425.87 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>281</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5-Aug GMP: 14</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7-Aug</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10-Aug</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>12-Aug</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5-Aug 16:32</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹255 (29.28%) 146 ↓ / 255 ↑</t>
+          <t>₹250 (28.70%) 146 ↓ / 253 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5-Aug 16:31</t>
+          <t>6-Aug 11:01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -549,61 +549,124 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Molbio Diagnostics IPOU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹185 (22.92%) 170 ↓ / 185 ↑</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>807</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹939.70 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>10-Aug</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12-Aug</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13-Aug</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>17-Aug</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6-Aug 10:59</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Ardee Industries IPOO</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹14 (26.42%) 6.50 ↓ / 14 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹14 (26.42%) 6.50 ↓ / 15.25 ↑</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>3.03x</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6.4x</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>53</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>₹425.87 Cr</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G4" t="n">
         <v>281</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>5-Aug GMP: 14</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>5-Aug GMP: 15.25</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>7-Aug</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>10-Aug</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>12-Aug</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>5-Aug 16:32</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6-Aug 10:54</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹250 (28.70%) 146 ↓ / 253 ↑</t>
+          <t>₹258 (29.62%) 146 ↓ / 258 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6-Aug 11:01</t>
+          <t>6-Aug 16:31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹185 (22.92%) 170 ↓ / 185 ↑</t>
+          <t>₹210 (26.02%) 170 ↓ / 210 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6-Aug 10:59</t>
+          <t>6-Aug 16:30</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹14 (26.42%) 6.50 ↓ / 15.25 ↑</t>
+          <t>₹15.5 (29.25%) 6.50 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.4x</t>
+          <t>14.4x</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>6-Aug 10:54</t>
+          <t>6-Aug 16:33</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOU</t>
+          <t>Molbio Diagnostics IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹258 (29.62%) 146 ↓ / 258 ↑</t>
+          <t>₹205 (25.40%) 170 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -505,15 +505,15 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>871</v>
+        <v>807</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6-Aug 16:31</t>
+          <t>7-Aug 10:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -549,12 +549,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOU</t>
+          <t>Dhoot Transmission IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹210 (26.02%) 170 ↓ / 210 ↑</t>
+          <t>₹255 (29.28%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,15 +568,15 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>807</v>
+        <v>871</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6-Aug 16:30</t>
+          <t>7-Aug 10:01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -612,12 +612,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOO</t>
+          <t>Ardee Industries IPOCT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹15.5 (29.25%) 6.50 ↓ / 15.50 ↑</t>
+          <t>₹13 (24.53%) 6.50 ↓ / 15.25 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>14.4x</t>
+          <t>17.5x</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>7-Aug GMP: 13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>6-Aug 16:33</t>
+          <t>7-Aug 9:58</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOU</t>
+          <t>Dhoot Transmission IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹205 (25.40%) 170 ↓ / 220 ↑</t>
+          <t>₹250 (28.70%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -505,15 +505,15 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>807</v>
+        <v>871</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7-Aug 10:02</t>
+          <t>7-Aug 15:36</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -549,12 +549,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOU</t>
+          <t>Ardee Industries IPOCT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹255 (29.28%) 146 ↓ / 259 ↑</t>
+          <t>₹13 (24.53%) 6.50 ↓ / 15.25 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -564,109 +564,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>134.55x</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>871</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>281</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>5-Aug GMP: 15.25</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7-Aug GMP: 13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>10-Aug</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>12-Aug</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>13-Aug</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>17-Aug</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7-Aug 10:01</t>
+          <t>7-Aug 15:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Ardee Industries IPOCT</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹13 (24.53%) 6.50 ↓ / 15.25 ↑</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>17.5x</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>53</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>₹425.87 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>281</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>5-Aug GMP: 15.25</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7-Aug GMP: 13</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>10-Aug</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>12-Aug</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>7-Aug 9:58</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹250 (28.70%) 146 ↓ / 259 ↑</t>
+          <t>₹247 (28.36%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,73 +537,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7-Aug 15:36</t>
+          <t>8-Aug 9:29</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ardee Industries IPOCT</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹13 (24.53%) 6.50 ↓ / 15.25 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>134.55x</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>53</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹425.87 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>281</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>5-Aug GMP: 15.25</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7-Aug GMP: 13</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>10-Aug</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>12-Aug</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>7-Aug 15:37</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹247 (28.36%) 146 ↓ / 259 ↑</t>
+          <t>₹250 (28.70%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8-Aug 9:29</t>
+          <t>8-Aug 14:54</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹250 (28.70%) 146 ↓ / 259 ↑</t>
+          <t>₹259 (29.74%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8-Aug 14:54</t>
+          <t>9-Aug 9:28</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,61 +486,124 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Shiprocket IPOU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹21 (21.65%) 14 ↓ / 21 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>97</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹1617.48 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>154</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>12-Aug</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>14-Aug</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>17-Aug</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>19-Aug</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>9-Aug 14:58</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Dhoot Transmission IPOU</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>₹259 (29.74%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>871</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>₹3066.89 Cr</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G3" t="n">
         <v>17</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>10-Aug</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>12-Aug</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>13-Aug</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>17-Aug</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>9-Aug 9:28</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>9-Aug 15:02</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹21 (21.65%) 14 ↓ / 21 ↑</t>
+          <t>₹22 (22.68%) 14 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>9-Aug 14:58</t>
+          <t>10-Aug 9:53</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -549,7 +549,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOU</t>
+          <t>Dhoot Transmission IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.03x</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>10-Aug GMP: 259</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>9-Aug 15:02</t>
+          <t>10-Aug 9:58</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹22 (22.68%) 14 ↓ / 22 ↑</t>
+          <t>₹26.5 (27.32%) 14 ↓ / 26.50 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10-Aug 9:53</t>
+          <t>10-Aug 15:36</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹259 (29.74%) 146 ↓ / 259 ↑</t>
+          <t>₹270 (31.00%) 146 ↓ / 270 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.03x</t>
+          <t>0.5x</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 259</t>
+          <t>10-Aug GMP: 270</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10-Aug 9:58</t>
+          <t>10-Aug 15:35</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹26.5 (27.32%) 14 ↓ / 26.50 ↑</t>
+          <t>₹27 (27.84%) 14 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10-Aug 15:36</t>
+          <t>11-Aug 9:29</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹270 (31.00%) 146 ↓ / 270 ↑</t>
+          <t>₹250 (28.70%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.5x</t>
+          <t>0.62x</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 270</t>
+          <t>10-Aug GMP: 250</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10-Aug 15:35</t>
+          <t>11-Aug 9:31</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>11-Aug 9:29</t>
+          <t>11-Aug 15:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹250 (28.70%) 146 ↓ / 259 ↑</t>
+          <t>₹246 (28.24%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.62x</t>
+          <t>3.41x</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>11-Aug 9:31</t>
+          <t>11-Aug 15:34</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Shiprocket IPOU</t>
+          <t>Behari Lal Engineering IPOO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹27 (27.84%) 14 ↓ / 27 ↑</t>
+          <t>₹67 (23.51%) 25 ↓ / 67 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,23 +501,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.16x</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>97</v>
+        <v>285</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>154</v>
+        <v>52</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>12-Aug GMP: 67</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>11-Aug 15:37</t>
+          <t>12-Aug 10:18</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -549,12 +549,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOO</t>
+          <t>Shiprocket IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹246 (28.24%) 146 ↓ / 259 ↑</t>
+          <t>₹31 (31.96%) 14 ↓ / 31 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -564,46 +564,109 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.41x</t>
+          <t>0.08x</t>
         </is>
       </c>
       <c r="E3" t="n">
+        <v>97</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹1617.48 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>154</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>12-Aug GMP: 31</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>14-Aug</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>17-Aug</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>19-Aug</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>12-Aug 10:20</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dhoot Transmission IPOCT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹258 (29.62%) 146 ↓ / 259 ↑</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5.06x</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>871</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>₹3066.89 Cr</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G4" t="n">
         <v>17</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>10-Aug GMP: 250</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12-Aug</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12-Aug GMP: 258</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>13-Aug</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>17-Aug</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>11-Aug 15:34</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>12-Aug 10:15</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹67 (23.51%) 25 ↓ / 67 ↑</t>
+          <t>₹70 (24.56%) 25 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.16x</t>
+          <t>1.82x</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -517,7 +517,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 67</t>
+          <t>12-Aug GMP: 70</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>12-Aug 10:18</t>
+          <t>12-Aug 15:31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹31 (31.96%) 14 ↓ / 31 ↑</t>
+          <t>₹32 (32.99%) 14 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.08x</t>
+          <t>0.79x</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 31</t>
+          <t>12-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12-Aug 10:20</t>
+          <t>12-Aug 15:35</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹258 (29.62%) 146 ↓ / 259 ↑</t>
+          <t>₹250 (28.70%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.06x</t>
+          <t>68.68x</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 258</t>
+          <t>12-Aug GMP: 250</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12-Aug 10:15</t>
+          <t>12-Aug 15:31</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOO</t>
+          <t>Lalithaa Jewellery Mart IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹70 (24.56%) 25 ↓ / 70 ↑</t>
+          <t>₹41 (20.40%) 17 ↓ / 41 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,43 +501,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.82x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>285</v>
+        <v>201</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 70</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>12-Aug 15:31</t>
+          <t>13-Aug 9:58</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹32 (32.99%) 14 ↓ / 32 ↑</t>
+          <t>₹34 (35.05%) 14 ↓ / 34 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.79x</t>
+          <t>1.2x</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 32</t>
+          <t>12-Aug GMP: 34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12-Aug 15:35</t>
+          <t>13-Aug 9:54</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -612,12 +612,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOCT</t>
+          <t>Behari Lal Engineering IPOO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹250 (28.70%) 146 ↓ / 259 ↑</t>
+          <t>₹74 (25.96%) 25 ↓ / 74 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -627,43 +627,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>68.68x</t>
+          <t>2.98x</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>871</v>
+        <v>285</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 250</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 250</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12-Aug 15:31</t>
+          <t>13-Aug 9:54</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOU</t>
+          <t>Shiprocket IPOO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹41 (20.40%) 17 ↓ / 41 ↑</t>
+          <t>₹34 (35.05%) 14 ↓ / 34 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,43 +501,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.92x</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>201</v>
+        <v>97</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>12-Aug GMP: 34</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>14-Aug</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>17-Aug</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>19-Aug</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>20-Aug</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>24-Aug</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>13-Aug 9:58</t>
+          <t>13-Aug 15:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -549,12 +549,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Shiprocket IPOO</t>
+          <t>Behari Lal Engineering IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹34 (35.05%) 14 ↓ / 34 ↑</t>
+          <t>₹78 (27.37%) 25 ↓ / 78 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -564,23 +564,23 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.2x</t>
+          <t>6.97x</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>97</v>
+        <v>285</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>154</v>
+        <v>52</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13-Aug 9:54</t>
+          <t>13-Aug 15:35</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -612,12 +612,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOO</t>
+          <t>Milky Mist Dairy Food IPOCT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹74 (25.96%) 25 ↓ / 74 ↑</t>
+          <t>₹30 (21.43%) 20.50 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -627,43 +627,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.98x</t>
+          <t>58.51x</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>285</v>
+        <v>140</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>11-Aug GMP: 22.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>13-Aug GMP: 30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>14-Aug</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>17-Aug</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>13-Aug 9:54</t>
+          <t>13-Aug 15:35</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Shiprocket IPOO</t>
+          <t>Behari Lal Engineering IPOCT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹34 (35.05%) 14 ↓ / 34 ↑</t>
+          <t>₹80 (28.07%) 25 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,28 +501,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.92x</t>
+          <t>8.47x</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>97</v>
+        <v>285</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>154</v>
+        <v>52</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>14-Aug GMP: 80</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>13-Aug 15:37</t>
+          <t>14-Aug 9:31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -549,12 +549,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOO</t>
+          <t>Shiprocket IPOCT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹78 (27.37%) 25 ↓ / 78 ↑</t>
+          <t>₹36.5 (37.63%) 14 ↓ / 36.50 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -564,28 +564,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6.97x</t>
+          <t>3.26x</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>285</v>
+        <v>97</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>52</v>
+        <v>154</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>12-Aug GMP: 34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>14-Aug GMP: 36.5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -600,73 +600,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13-Aug 15:35</t>
+          <t>14-Aug 9:34</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Milky Mist Dairy Food IPOCT</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹30 (21.43%) 20.50 ↓ / 30 ↑</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>58.51x</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>140</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>₹1553.00 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>107</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>11-Aug GMP: 22.5</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>13-Aug GMP: 30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>14-Aug</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>18-Aug</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>13-Aug 15:35</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOCT</t>
+          <t>Shiprocket IPOCT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹80 (28.07%) 25 ↓ / 80 ↑</t>
+          <t>₹37 (38.14%) 14 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,28 +501,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.47x</t>
+          <t>89.78x</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>285</v>
+        <v>97</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>52</v>
+        <v>154</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>12-Aug GMP: 34</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 80</t>
+          <t>14-Aug GMP: 37</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>14-Aug 9:31</t>
+          <t>14-Aug 15:33</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -549,12 +549,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Shiprocket IPOCT</t>
+          <t>Behari Lal Engineering IPOCT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹36.5 (37.63%) 14 ↓ / 36.50 ↑</t>
+          <t>₹83 (29.12%) 25 ↓ / 83 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -564,28 +564,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.26x</t>
+          <t>103.8x</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>97</v>
+        <v>285</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>154</v>
+        <v>52</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 36.5</t>
+          <t>14-Aug GMP: 83</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>14-Aug 9:34</t>
+          <t>14-Aug 15:30</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Shiprocket IPOCT</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹37 (38.14%) 14 ↓ / 37 ↑</t>
+          <t>₹28 (20.29%) 19 ↓ / 28 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,109 +501,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>89.78x</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>97</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>154</v>
+          <t>₹582.80 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 37</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>14-Aug 15:33</t>
+          <t>15-Aug 8:56</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Behari Lal Engineering IPOCT</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹83 (29.12%) 25 ↓ / 83 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>103.8x</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>285</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹301.62 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>52</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>12-Aug GMP: 74</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>14-Aug GMP: 83</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>17-Aug</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>19-Aug</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>14-Aug 15:30</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>15-Aug 8:56</t>
+          <t>15-Aug 14:58</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>15-Aug 14:58</t>
+          <t>16-Aug 8:53</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16-Aug 8:53</t>
+          <t>16-Aug 15:01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,10 +541,77 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16-Aug 15:01</t>
+          <t>17-Aug 8:54</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tempsens Instruments (India) IPOU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹65 (21.67%) 65 ↓ / 85 ↑</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹650.00 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20-Aug</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>24-Aug</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>25-Aug</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>28-Aug</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>17-Aug 8:56</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹28 (20.29%) 19 ↓ / 28 ↑</t>
+          <t>₹30 (21.74%) 19 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>17-Aug 8:54</t>
+          <t>17-Aug 15:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹65 (21.67%) 65 ↓ / 85 ↑</t>
+          <t>₹130 (43.33%) 65 ↓ / 130 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>17-Aug 8:56</t>
+          <t>17-Aug 14:59</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹30 (21.74%) 19 ↓ / 30 ↑</t>
+          <t>₹31 (22.46%) 19 ↓ / 31 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>17-Aug 15:00</t>
+          <t>18-Aug 8:55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,60 +558,127 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹130 (43.33%) 65 ↓ / 130 ↑</t>
+          <t>₹154 (51.33%) 65 ↓ / 154 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>🔥🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹650.00 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20-Aug</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>24-Aug</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>25-Aug</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>28-Aug</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>18-Aug 8:57</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sunshine Pictures IPOO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹75 (20.83%) 17 ↓ / 75 ↑</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹650.00 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>₹282.14 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>18-Aug GMP: 75</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>20-Aug</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>24-Aug</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>21-Aug</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>25-Aug</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>28-Aug</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>17-Aug 14:59</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>18-Aug 8:53</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>18-Aug 8:55</t>
+          <t>18-Aug 14:58</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,17 +553,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOU</t>
+          <t>Augmont Enterprises IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹154 (51.33%) 65 ↓ / 154 ↑</t>
+          <t>₹165 (20.94%) 165 ↓ / 165 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -573,42 +573,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18-Aug 8:57</t>
+          <t>18-Aug 15:01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,65 +620,132 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Tempsens Instruments (India) IPOU</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹158 (52.67%) 65 ↓ / 158 ↑</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>₹650.00 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>20-Aug</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>24-Aug</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>25-Aug</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>28-Aug</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>18-Aug 15:00</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Sunshine Pictures IPOO</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>₹75 (20.83%) 17 ↓ / 75 ↑</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3.24x</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>360</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>₹282.14 Cr</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>18-Aug GMP: 75</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>20-Aug</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>21-Aug</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>25-Aug</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>18-Aug 8:53</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>18-Aug 14:56</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹31 (22.46%) 19 ↓ / 31 ↑</t>
+          <t>₹40 (28.99%) 19 ↓ / 40 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>18-Aug 14:58</t>
+          <t>19-Aug 9:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹165 (20.94%) 165 ↓ / 165 ↑</t>
+          <t>₹190 (24.11%) 190 ↓ / 190 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18-Aug 15:01</t>
+          <t>19-Aug 8:56</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹158 (52.67%) 65 ↓ / 158 ↑</t>
+          <t>₹172 (57.33%) 65 ↓ / 172 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>18-Aug 15:00</t>
+          <t>19-Aug 9:01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹75 (20.83%) 17 ↓ / 75 ↑</t>
+          <t>₹77 (21.39%) 17 ↓ / 77 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.24x</t>
+          <t>4.34x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 75</t>
+          <t>18-Aug GMP: 77</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>18-Aug 14:56</t>
+          <t>19-Aug 8:56</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19-Aug 9:00</t>
+          <t>19-Aug 14:53</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19-Aug 8:56</t>
+          <t>19-Aug 14:56</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹172 (57.33%) 65 ↓ / 172 ↑</t>
+          <t>₹185 (61.67%) 65 ↓ / 185 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19-Aug 9:01</t>
+          <t>19-Aug 14:58</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹77 (21.39%) 17 ↓ / 77 ↑</t>
+          <t>₹78 (21.67%) 17 ↓ / 78 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.34x</t>
+          <t>15.39x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -742,10 +742,77 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>19-Aug 8:56</t>
+          <t>19-Aug 15:00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lalithaa Jewellery Mart IPOCT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>₹44 (21.89%) 17 ↓ / 44 ↑</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>44.16x</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>₹1700.00 Cr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>17-Aug GMP: 30</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19-Aug GMP: 44</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>20-Aug</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>24-Aug</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>19-Aug 14:57</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹40 (28.99%) 19 ↓ / 40 ↑</t>
+          <t>₹42 (30.43%) 19 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19-Aug 14:53</t>
+          <t>20-Aug 9:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOU</t>
+          <t>Symbiotec Pharmalab IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹190 (24.11%) 190 ↓ / 190 ↑</t>
+          <t>₹220 (22.27%) 220 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -573,42 +573,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19-Aug 14:56</t>
+          <t>20-Aug 9:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,17 +620,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOU</t>
+          <t>Augmont Enterprises IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹185 (61.67%) 65 ↓ / 185 ↑</t>
+          <t>₹280 (35.53%) 190 ↓ / 280 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -640,42 +640,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19-Aug 14:58</t>
+          <t>20-Aug 8:56</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,62 +687,62 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOO</t>
+          <t>Tempsens Instruments (India) IPOO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹78 (21.67%) 17 ↓ / 78 ↑</t>
+          <t>₹220 (73.33%) 65 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15.39x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 77</t>
+          <t>20-Aug GMP: 220</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>19-Aug 15:00</t>
+          <t>20-Aug 8:55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOCT</t>
+          <t>Sunshine Pictures IPOCT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹44 (21.89%) 17 ↓ / 44 ↑</t>
+          <t>₹77 (21.39%) 17 ↓ / 77 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -769,47 +769,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.16x</t>
+          <t>18.47x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 30</t>
+          <t>18-Aug GMP: 77</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 44</t>
+          <t>20-Aug GMP: 77</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>19-Aug 14:57</t>
+          <t>20-Aug 8:55</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20-Aug 9:00</t>
+          <t>20-Aug 14:55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹220 (22.27%) 220 ↓ / 220 ↑</t>
+          <t>₹240 (24.29%) 220 ↓ / 240 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20-Aug 9:02</t>
+          <t>20-Aug 14:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹280 (35.53%) 190 ↓ / 280 ↑</t>
+          <t>₹285 (36.17%) 190 ↓ / 285 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20-Aug 8:56</t>
+          <t>20-Aug 15:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹220 (73.33%) 65 ↓ / 220 ↑</t>
+          <t>₹232 (77.33%) 65 ↓ / 232 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.8x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 220</t>
+          <t>20-Aug GMP: 232</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>20-Aug 8:55</t>
+          <t>20-Aug 14:53</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹77 (21.39%) 17 ↓ / 77 ↑</t>
+          <t>₹79 (21.94%) 17 ↓ / 79 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18.47x</t>
+          <t>84.51x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 77</t>
+          <t>20-Aug GMP: 79</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>20-Aug 8:55</t>
+          <t>20-Aug 15:02</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹42 (30.43%) 19 ↓ / 42 ↑</t>
+          <t>₹42 (30.43%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20-Aug 14:55</t>
+          <t>21-Aug 8:33</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹240 (24.29%) 220 ↓ / 240 ↑</t>
+          <t>₹320 (32.39%) 220 ↓ / 320 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20-Aug 14:55</t>
+          <t>21-Aug 8:32</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOU</t>
+          <t>Hy-Tech Engineers IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹285 (36.17%) 190 ↓ / 285 ↑</t>
+          <t>₹22 (41.51%) 5 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -640,42 +640,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20-Aug 15:00</t>
+          <t>21-Aug 8:32</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,62 +687,62 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOO</t>
+          <t>Augmont Enterprises IPOO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹232 (77.33%) 65 ↓ / 232 ↑</t>
+          <t>₹300 (38.07%) 190 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.8x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 232</t>
+          <t>21-Aug GMP: 300</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>20-Aug 14:53</t>
+          <t>21-Aug 8:29</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -754,62 +754,62 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOCT</t>
+          <t>Tempsens Instruments (India) IPOO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹79 (21.94%) 17 ↓ / 79 ↑</t>
+          <t>₹270 (90.00%) 65 ↓ / 270 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>84.51x</t>
+          <t>5.95x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 77</t>
+          <t>20-Aug GMP: 270</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 79</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>20-Aug 15:02</t>
+          <t>21-Aug 8:31</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,17 +486,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>Lumino Industries IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹42 (30.43%) 19 ↓ / 50 ↑</t>
+          <t>₹45 (54.88%) 45 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -506,42 +506,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹700.00 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>21-Aug 8:33</t>
+          <t>21-Aug 14:57</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>21-Aug 8:32</t>
+          <t>21-Aug 15:01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>21-Aug 8:32</t>
+          <t>21-Aug 14:53</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,12 +687,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOO</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹300 (38.07%) 190 ↓ / 300 ↑</t>
+          <t>₹45 (32.61%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -707,42 +707,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 300</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>21-Aug 8:29</t>
+          <t>21-Aug 14:59</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -754,65 +754,132 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Augmont Enterprises IPOO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>₹300 (38.07%) 190 ↓ / 300 ↑</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.77x</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>₹825.00 Cr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>21-Aug GMP: 300</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25-Aug</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>27-Aug</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>31-Aug</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>21-Aug 14:55</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Tempsens Instruments (India) IPOO</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>₹270 (90.00%) 65 ↓ / 270 ↑</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>₹277 (92.33%) 65 ↓ / 277 ↑</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>5.95x</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>18.02x</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>₹650.00 Cr</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>20-Aug GMP: 270</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>24-Aug</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>25-Aug</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>28-Aug</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>21-Aug 8:31</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>21-Aug 14:58</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹45 (54.88%) 45 ↓ / 45 ↑</t>
+          <t>₹46 (56.10%) 46 ↓ / 46 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>21-Aug 14:57</t>
+          <t>22-Aug 8:59</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹320 (32.39%) 220 ↓ / 320 ↑</t>
+          <t>₹345 (34.92%) 220 ↓ / 345 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>21-Aug 15:01</t>
+          <t>22-Aug 8:57</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>21-Aug 14:53</t>
+          <t>22-Aug 9:01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>21-Aug 14:59</t>
+          <t>22-Aug 9:00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹300 (38.07%) 190 ↓ / 300 ↑</t>
+          <t>₹310 (39.34%) 190 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.77x</t>
+          <t>2.88x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 300</t>
+          <t>21-Aug GMP: 310</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>21-Aug 14:55</t>
+          <t>22-Aug 9:00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹277 (92.33%) 65 ↓ / 277 ↑</t>
+          <t>₹290 (96.67%) 65 ↓ / 290 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18.02x</t>
+          <t>21.69x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21-Aug 14:58</t>
+          <t>22-Aug 8:57</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>22-Aug 8:59</t>
+          <t>22-Aug 14:53</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹345 (34.92%) 220 ↓ / 345 ↑</t>
+          <t>₹365 (36.94%) 220 ↓ / 365 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>22-Aug 8:57</t>
+          <t>22-Aug 14:58</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹22 (41.51%) 5 ↓ / 22 ↑</t>
+          <t>₹25 (47.17%) 5 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>22-Aug 9:01</t>
+          <t>22-Aug 15:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹45 (32.61%) 19 ↓ / 50 ↑</t>
+          <t>₹42 (30.43%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>22-Aug 9:00</t>
+          <t>22-Aug 14:56</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹310 (39.34%) 190 ↓ / 310 ↑</t>
+          <t>₹370 (46.95%) 190 ↓ / 370 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>22-Aug 9:00</t>
+          <t>22-Aug 14:57</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹290 (96.67%) 65 ↓ / 290 ↑</t>
+          <t>₹315 (105.00%) 65 ↓ / 315 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>22-Aug 8:57</t>
+          <t>22-Aug 15:01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹46 (56.10%) 46 ↓ / 46 ↑</t>
+          <t>₹52 (63.41%) 46 ↓ / 52 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>22-Aug 14:53</t>
+          <t>23-Aug 8:56</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOU</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹365 (36.94%) 220 ↓ / 365 ↑</t>
+          <t>₹37 (26.81%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>22-Aug 14:58</t>
+          <t>23-Aug 8:57</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,12 +625,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹25 (47.17%) 5 ↓ / 25 ↑</t>
+          <t>₹27 (50.94%) 5 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>22-Aug 15:00</t>
+          <t>23-Aug 8:58</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,12 +687,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>Symbiotec Pharmalab IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹42 (30.43%) 19 ↓ / 50 ↑</t>
+          <t>₹410 (41.50%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>22-Aug 14:56</t>
+          <t>23-Aug 8:53</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹370 (46.95%) 190 ↓ / 370 ↑</t>
+          <t>₹395 (50.13%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>22-Aug 14:57</t>
+          <t>23-Aug 8:53</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹315 (105.00%) 65 ↓ / 315 ↑</t>
+          <t>₹321 (107.00%) 65 ↓ / 321 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>22-Aug 15:01</t>
+          <t>23-Aug 9:01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>23-Aug 8:56</t>
+          <t>23-Aug 15:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹37 (26.81%) 19 ↓ / 50 ↑</t>
+          <t>₹34 (24.64%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>23-Aug 8:57</t>
+          <t>23-Aug 14:53</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹27 (50.94%) 5 ↓ / 27 ↑</t>
+          <t>₹29 (54.72%) 5 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>23-Aug 8:58</t>
+          <t>23-Aug 15:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹410 (41.50%) 220 ↓ / 410 ↑</t>
+          <t>₹409 (41.40%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>23-Aug 8:53</t>
+          <t>23-Aug 14:55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹395 (50.13%) 190 ↓ / 395 ↑</t>
+          <t>₹380 (48.22%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>23-Aug 8:53</t>
+          <t>23-Aug 15:01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23-Aug 9:01</t>
+          <t>23-Aug 14:53</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹52 (63.41%) 46 ↓ / 52 ↑</t>
+          <t>₹49 (59.76%) 46 ↓ / 52 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>23-Aug 15:00</t>
+          <t>24-Aug 8:54</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>Skyways Air IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹34 (24.64%) 19 ↓ / 50 ↑</t>
+          <t>₹32 (23.19%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>24-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>23-Aug 14:53</t>
+          <t>24-Aug 8:53</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,17 +620,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOU</t>
+          <t>Symbiotec Pharmalab IPOO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹29 (54.72%) 5 ↓ / 29 ↑</t>
+          <t>₹409 (41.40%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -640,22 +640,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>24-Aug GMP: 409</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>23-Aug 15:00</t>
+          <t>24-Aug 8:53</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,12 +687,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOU</t>
+          <t>Hy-Tech Engineers IPOO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹409 (41.40%) 220 ↓ / 410 ↑</t>
+          <t>₹25 (47.17%) 5 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -707,22 +707,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>24-Aug GMP: 25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>23-Aug 14:55</t>
+          <t>24-Aug 8:57</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>23-Aug 15:01</t>
+          <t>24-Aug 8:59</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -821,12 +821,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOO</t>
+          <t>Tempsens Instruments (India) IPOCT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹321 (107.00%) 65 ↓ / 321 ↑</t>
+          <t>₹313 (104.33%) 65 ↓ / 321 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>24-Aug GMP: 313</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23-Aug 14:53</t>
+          <t>24-Aug 8:57</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹49 (59.76%) 46 ↓ / 52 ↑</t>
+          <t>₹46 (56.10%) 46 ↓ / 52 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>24-Aug 8:54</t>
+          <t>24-Aug 14:59</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹32 (23.19%) 19 ↓ / 50 ↑</t>
+          <t>₹33 (23.91%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.92x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 32</t>
+          <t>24-Aug GMP: 33</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>24-Aug 8:53</t>
+          <t>24-Aug 14:57</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,42 +620,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOO</t>
+          <t>Hy-Tech Engineers IPOO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹409 (41.40%) 220 ↓ / 410 ↑</t>
+          <t>₹35 (66.04%) 5 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.08x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 409</t>
+          <t>24-Aug GMP: 35</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>24-Aug 8:53</t>
+          <t>24-Aug 14:57</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,12 +687,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOO</t>
+          <t>Symbiotec Pharmalab IPOO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹25 (47.17%) 5 ↓ / 27 ↑</t>
+          <t>₹388 (39.27%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,27 +702,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.69x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 25</t>
+          <t>24-Aug GMP: 388</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>24-Aug 8:57</t>
+          <t>24-Aug 14:53</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹380 (48.22%) 190 ↓ / 395 ↑</t>
+          <t>₹372 (47.21%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.88x</t>
+          <t>12.99x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>24-Aug 8:59</t>
+          <t>24-Aug 15:00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹313 (104.33%) 65 ↓ / 321 ↑</t>
+          <t>₹325 (108.33%) 65 ↓ / 325 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21.69x</t>
+          <t>160.21x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 313</t>
+          <t>24-Aug GMP: 325</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24-Aug 8:57</t>
+          <t>24-Aug 15:01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,17 +486,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lumino Industries IPOU</t>
+          <t>ESDS Software Solution IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹46 (56.10%) 46 ↓ / 52 ↑</t>
+          <t>₹130 (30.30%) 130 ↓ / 130 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -506,42 +506,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>429</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹700.00 Cr</t>
+          <t>₹720.00 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>24-Aug 14:59</t>
+          <t>25-Aug 8:58</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,62 +553,62 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Skyways Air IPOO</t>
+          <t>Lumino Industries IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹33 (23.91%) 19 ↓ / 50 ↑</t>
+          <t>₹47 (57.32%) 46 ↓ / 52 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.92x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹700.00 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 33</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>24-Aug 14:57</t>
+          <t>25-Aug 8:58</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,42 +620,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOO</t>
+          <t>Skyways Air IPOO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹35 (66.04%) 5 ↓ / 35 ↑</t>
+          <t>₹32 (23.19%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.08x</t>
+          <t>1.16x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 35</t>
+          <t>24-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>24-Aug 14:57</t>
+          <t>25-Aug 8:59</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,42 +687,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOO</t>
+          <t>Hy-Tech Engineers IPOO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹388 (39.27%) 220 ↓ / 410 ↑</t>
+          <t>₹30 (56.60%) 5 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.69x</t>
+          <t>7.84x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 388</t>
+          <t>24-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>24-Aug 14:53</t>
+          <t>25-Aug 8:57</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOO</t>
+          <t>Symbiotec Pharmalab IPOO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹372 (47.21%) 190 ↓ / 395 ↑</t>
+          <t>₹340 (34.41%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -769,47 +769,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12.99x</t>
+          <t>0.85x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 310</t>
+          <t>24-Aug GMP: 335</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>24-Aug 15:00</t>
+          <t>25-Aug 8:57</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -821,62 +821,62 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOCT</t>
+          <t>Augmont Enterprises IPOCT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹325 (108.33%) 65 ↓ / 325 ↑</t>
+          <t>₹325 (41.24%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>160.21x</t>
+          <t>15.21x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 270</t>
+          <t>21-Aug GMP: 310</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 325</t>
+          <t>25-Aug GMP: 325</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24-Aug 15:01</t>
+          <t>25-Aug 8:55</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹130 (30.30%) 130 ↓ / 130 ↑</t>
+          <t>₹255 (59.44%) 255 ↓ / 255 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>25-Aug 8:58</t>
+          <t>25-Aug 15:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹47 (57.32%) 46 ↓ / 52 ↑</t>
+          <t>₹49 (59.76%) 46 ↓ / 52 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25-Aug 8:58</t>
+          <t>25-Aug 14:57</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,42 +620,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Skyways Air IPOO</t>
+          <t>Hy-Tech Engineers IPOO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹32 (23.19%) 19 ↓ / 50 ↑</t>
+          <t>₹30 (56.60%) 5 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.16x</t>
+          <t>17x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 32</t>
+          <t>24-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25-Aug 8:59</t>
+          <t>25-Aug 14:58</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,42 +687,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOO</t>
+          <t>Skyways Air IPOO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹30 (56.60%) 5 ↓ / 30 ↑</t>
+          <t>₹29 (21.01%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.84x</t>
+          <t>2.16x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 30</t>
+          <t>24-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25-Aug 8:57</t>
+          <t>25-Aug 15:01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹340 (34.41%) 220 ↓ / 410 ↑</t>
+          <t>₹350 (35.43%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.85x</t>
+          <t>1.68x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25-Aug 8:57</t>
+          <t>25-Aug 14:53</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹325 (41.24%) 190 ↓ / 395 ↑</t>
+          <t>₹320 (40.61%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15.21x</t>
+          <t>90.36x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 325</t>
+          <t>25-Aug GMP: 320</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25-Aug 8:55</t>
+          <t>25-Aug 15:01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹255 (59.44%) 255 ↓ / 255 ↑</t>
+          <t>₹280 (65.27%) 275 ↓ / 280 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>25-Aug 15:02</t>
+          <t>26-Aug 8:53</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹49 (59.76%) 46 ↓ / 52 ↑</t>
+          <t>₹46 (56.10%) 46 ↓ / 52 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25-Aug 14:57</t>
+          <t>26-Aug 8:59</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,42 +620,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOO</t>
+          <t>Symbiotec Pharmalab IPOO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹30 (56.60%) 5 ↓ / 30 ↑</t>
+          <t>₹352 (35.63%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>17x</t>
+          <t>1.95x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 30</t>
+          <t>24-Aug GMP: 335</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25-Aug 14:58</t>
+          <t>26-Aug 9:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.16x</t>
+          <t>2.46x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25-Aug 15:01</t>
+          <t>26-Aug 8:58</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -754,42 +754,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOO</t>
+          <t>Hy-Tech Engineers IPOO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹350 (35.43%) 220 ↓ / 410 ↑</t>
+          <t>₹30 (56.60%) 5 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.68x</t>
+          <t>19.57x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 335</t>
+          <t>24-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -809,77 +809,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25-Aug 14:53</t>
+          <t>26-Aug 8:59</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Augmont Enterprises IPOCT</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>₹320 (40.61%) 190 ↓ / 395 ↑</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>90.36x</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>₹825.00 Cr</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>21-Aug GMP: 310</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25-Aug GMP: 320</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>27-Aug</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>31-Aug</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>25-Aug 15:01</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹280 (65.27%) 275 ↓ / 280 ↑</t>
+          <t>₹330 (76.92%) 275 ↓ / 330 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>26-Aug 8:53</t>
+          <t>26-Aug 14:34</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>26-Aug 8:59</t>
+          <t>26-Aug 14:28</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹352 (35.63%) 220 ↓ / 410 ↑</t>
+          <t>₹340 (34.41%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.95x</t>
+          <t>4.69x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>26-Aug 9:00</t>
+          <t>26-Aug 14:32</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.46x</t>
+          <t>4.46x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>26-Aug 8:58</t>
+          <t>26-Aug 14:32</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹30 (56.60%) 5 ↓ / 30 ↑</t>
+          <t>₹40 (75.47%) 5 ↓ / 40 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19.57x</t>
+          <t>44.31x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>26-Aug 8:59</t>
+          <t>26-Aug 14:35</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹330 (76.92%) 275 ↓ / 330 ↑</t>
+          <t>₹335 (78.09%) 275 ↓ / 365 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>26-Aug 14:34</t>
+          <t>27-Aug 16:36</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lumino Industries IPOU</t>
+          <t>Lumino Industries IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹46 (56.10%) 46 ↓ / 52 ↑</t>
+          <t>₹56 (68.29%) 46 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.35x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>27-Aug GMP: 56</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>26-Aug 14:28</t>
+          <t>27-Aug 16:28</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOO</t>
+          <t>Symbiotec Pharmalab IPOCT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹340 (34.41%) 220 ↓ / 410 ↑</t>
+          <t>₹265 (26.82%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.69x</t>
+          <t>74.98x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>27-Aug GMP: 265</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>26-Aug 14:32</t>
+          <t>27-Aug 16:30</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,12 +687,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Skyways Air IPOO</t>
+          <t>Skyways Air IPOCT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹29 (21.01%) 19 ↓ / 50 ↑</t>
+          <t>₹45 (32.61%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.46x</t>
+          <t>71.01x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>27-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>26-Aug 14:32</t>
+          <t>27-Aug 16:31</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOO</t>
+          <t>Hy-Tech Engineers IPOCT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹40 (75.47%) 5 ↓ / 40 ↑</t>
+          <t>₹45 (84.91%) 5 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.31x</t>
+          <t>246.27x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>27-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>26-Aug 14:35</t>
+          <t>27-Aug 16:32</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,17 +486,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ESDS Software Solution IPOU</t>
+          <t>Deepa Jewellers IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹335 (78.09%) 275 ↓ / 365 ↑</t>
+          <t>₹43 (24.29%) 43 ↓ / 43 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -506,42 +506,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹720.00 Cr</t>
+          <t>₹459.72 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27-Aug 16:36</t>
+          <t>27-Aug 19:28</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lumino Industries IPOO</t>
+          <t>ESDS Software Solution IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹56 (68.29%) 46 ↓ / 56 ↑</t>
+          <t>₹336 (78.32%) 275 ↓ / 365 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,47 +568,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.35x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>429</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹700.00 Cr</t>
+          <t>₹720.00 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 56</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-Aug 16:28</t>
+          <t>27-Aug 19:34</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,199 +620,65 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOCT</t>
+          <t>Lumino Industries IPOO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹265 (26.82%) 220 ↓ / 410 ↑</t>
+          <t>₹55 (67.07%) 46 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>74.98x</t>
+          <t>1.51x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹700.00 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 335</t>
+          <t>27-Aug GMP: 55</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 265</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>27-Aug 16:30</t>
+          <t>27-Aug 19:34</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Skyways Air IPOCT</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>₹45 (32.61%) 19 ↓ / 50 ↑</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>71.01x</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>₹582.80 Cr</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>24-Aug GMP: 32</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>27-Aug GMP: 45</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>28-Aug</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>1-Sep</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>27-Aug 16:31</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Hy-Tech Engineers IPOCT</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>₹45 (84.91%) 5 ↓ / 45 ↑</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>246.27x</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>₹135.73 Cr</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>24-Aug GMP: 30</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>27-Aug GMP: 45</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>28-Aug</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>1-Sep</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>27-Aug 16:32</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹43 (24.29%) 43 ↓ / 43 ↑</t>
+          <t>₹47 (26.55%) 47 ↓ / 47 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27-Aug 19:28</t>
+          <t>28-Aug 20:32</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ESDS Software Solution IPOU</t>
+          <t>ESDS Software Solution IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹336 (78.32%) 275 ↓ / 365 ↑</t>
+          <t>₹380 (88.58%) 275 ↓ / 380 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.21x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>28-Aug GMP: 380</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-Aug 19:34</t>
+          <t>28-Aug 20:33</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,65 +620,132 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Priority Jewels IPOO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹45 (22.50%) 20 ↓ / 45 ↑</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.93x</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>₹91.50 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>28-Aug GMP: 45</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1-Sep</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2-Sep</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>4-Sep</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>28-Aug 20:32</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Lumino Industries IPOO</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹55 (67.07%) 46 ↓ / 55 ↑</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>₹59 (71.95%) 46 ↓ / 59 ↑</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1.51x</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5.14x</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>₹700.00 Cr</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>182</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>27-Aug GMP: 55</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>27-Aug GMP: 56</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>31-Aug</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>1-Sep</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>3-Sep</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>27-Aug 19:34</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>28-Aug 20:35</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹47 (26.55%) 47 ↓ / 47 ↑</t>
+          <t>₹53 (29.94%) 47 ↓ / 53 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>28-Aug 20:32</t>
+          <t>29-Aug 15:01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 380</t>
+          <t>28-Aug GMP: 360</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>28-Aug 20:33</t>
+          <t>29-Aug 14:54</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹45 (22.50%) 20 ↓ / 45 ↑</t>
+          <t>₹47 (23.50%) 20 ↓ / 47 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>28-Aug 20:32</t>
+          <t>29-Aug 14:54</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹59 (71.95%) 46 ↓ / 59 ↑</t>
+          <t>₹61 (74.39%) 46 ↓ / 61.50 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>28-Aug 20:35</t>
+          <t>29-Aug 14:54</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹53 (29.94%) 47 ↓ / 53 ↑</t>
+          <t>₹43 (24.29%) 43 ↓ / 53 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>29-Aug 15:01</t>
+          <t>30-Aug 14:31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹380 (88.58%) 275 ↓ / 380 ↑</t>
+          <t>₹372 (86.71%) 275 ↓ / 372 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>29-Aug 14:54</t>
+          <t>30-Aug 14:33</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹47 (23.50%) 20 ↓ / 47 ↑</t>
+          <t>₹45 (22.50%) 20 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>29-Aug 14:54</t>
+          <t>30-Aug 14:28</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹61 (74.39%) 46 ↓ / 61.50 ↑</t>
+          <t>₹62 (75.61%) 46 ↓ / 63 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>29-Aug 14:54</t>
+          <t>30-Aug 14:31</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹43 (24.29%) 43 ↓ / 53 ↑</t>
+          <t>₹45 (25.42%) 45 ↓ / 53 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>30-Aug 14:31</t>
+          <t>30-Aug 19:31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹372 (86.71%) 275 ↓ / 372 ↑</t>
+          <t>₹355 (82.75%) 275 ↓ / 372 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>30-Aug 14:33</t>
+          <t>30-Aug 19:36</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>30-Aug 14:28</t>
+          <t>30-Aug 19:32</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹62 (75.61%) 46 ↓ / 63 ↑</t>
+          <t>₹60 (73.17%) 46 ↓ / 63 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>30-Aug 14:31</t>
+          <t>30-Aug 19:32</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹45 (25.42%) 45 ↓ / 53 ↑</t>
+          <t>₹42 (23.73%) 42 ↓ / 53 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>30-Aug 19:31</t>
+          <t>31-Aug 14:53</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹355 (82.75%) 275 ↓ / 372 ↑</t>
+          <t>₹324 (75.52%) 275 ↓ / 372 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.21x</t>
+          <t>20.75x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>30-Aug 19:36</t>
+          <t>31-Aug 14:53</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.93x</t>
+          <t>22.35x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>30-Aug 19:32</t>
+          <t>31-Aug 14:55</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,12 +687,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lumino Industries IPOO</t>
+          <t>Lumino Industries IPOCT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹60 (73.17%) 46 ↓ / 63 ↑</t>
+          <t>₹54 (65.85%) 46 ↓ / 63 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.14x</t>
+          <t>67.01x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>31-Aug GMP: 54</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>30-Aug 19:32</t>
+          <t>31-Aug 15:01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Deepa Jewellers IPOU</t>
+          <t>Rays of Belief IPOO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹42 (23.73%) 42 ↓ / 53 ↑</t>
+          <t>₹48 (20.08%) 10 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,27 +501,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.83x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>239</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹459.72 Cr</t>
+          <t>₹125.00 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>1-Sep GMP: 48</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>31-Aug 14:53</t>
+          <t>1-Sep 14:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,62 +553,62 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ESDS Software Solution IPOO</t>
+          <t>Deepa Jewellers IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹324 (75.52%) 275 ↓ / 372 ↑</t>
+          <t>₹44 (24.86%) 44 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20.75x</t>
+          <t>0.6x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹720.00 Cr</t>
+          <t>₹459.72 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 360</t>
+          <t>1-Sep GMP: 44</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>31-Aug 14:53</t>
+          <t>1-Sep 13:59</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,47 +620,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Priority Jewels IPOO</t>
+          <t>ESDS Software Solution IPOCT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹45 (22.50%) 20 ↓ / 45 ↑</t>
+          <t>₹257 (59.91%) 257 ↓ / 372 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>22.35x</t>
+          <t>67.26x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>429</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹91.50 Cr</t>
+          <t>₹720.00 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 45</t>
+          <t>28-Aug GMP: 360</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>1-Sep GMP: 257</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>31-Aug 14:55</t>
+          <t>1-Sep 13:57</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,62 +687,62 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lumino Industries IPOCT</t>
+          <t>Priority Jewels IPOCT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹54 (65.85%) 46 ↓ / 63 ↑</t>
+          <t>₹40 (20.00%) 20 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>67.01x</t>
+          <t>71.02x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹700.00 Cr</t>
+          <t>₹91.50 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 56</t>
+          <t>28-Aug GMP: 45</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 54</t>
+          <t>1-Sep GMP: 40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>31-Aug 15:01</t>
+          <t>1-Sep 13:59</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rays of Belief IPOO</t>
+          <t>Deepa Jewellers IPOO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹48 (20.08%) 10 ↓ / 48 ↑</t>
+          <t>₹44 (24.86%) 44 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,27 +501,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83x</t>
+          <t>0.88x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹125.00 Cr</t>
+          <t>₹459.72 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 48</t>
+          <t>1-Sep GMP: 44</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,211 +541,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1-Sep 14:00</t>
+          <t>1-Sep 18:55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Deepa Jewellers IPOO</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹44 (24.86%) 44 ↓ / 55 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.6x</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹459.72 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1-Sep GMP: 44</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3-Sep</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>4-Sep</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>8-Sep</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1-Sep 13:59</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ESDS Software Solution IPOCT</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹257 (59.91%) 257 ↓ / 372 ↑</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>67.26x</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>₹720.00 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>28-Aug GMP: 360</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1-Sep GMP: 257</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2-Sep</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>4-Sep</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1-Sep 13:57</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Priority Jewels IPOCT</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>₹40 (20.00%) 20 ↓ / 45 ↑</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>71.02x</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>₹91.50 Cr</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>28-Aug GMP: 45</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1-Sep GMP: 40</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2-Sep</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>4-Sep</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1-Sep 13:59</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Deepa Jewellers IPOO</t>
+          <t>Pranav Constructions IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹44 (24.86%) 44 ↓ / 55 ↑</t>
+          <t>₹25 (20.16%) 23 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,47 +501,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹459.72 Cr</t>
+          <t>₹351.03 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 44</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>10-Sep</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1-Sep 18:55</t>
+          <t>2-Sep 13:01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹25 (20.16%) 23 ↓ / 25 ↑</t>
+          <t>₹27 (21.77%) 23 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2-Sep 13:01</t>
+          <t>2-Sep 18:28</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,65 +486,199 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Kanohar Electricals IPOU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹150 (23.73%) 150 ↓ / 150 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹1055.74 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>8-Sep</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>3-Sep 12:57</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Pranav Constructions IPOU</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>₹27 (21.77%) 23 ↓ / 27 ↑</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>124</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>₹351.03 Cr</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>7-Sep</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>9-Sep</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>10-Sep</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>15-Sep</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2-Sep 18:28</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>3-Sep 13:00</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Rays of Belief IPOCT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹63 (26.36%) 10 ↓ / 63 ↑</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>36.74x</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>₹125.00 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1-Sep GMP: 38</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3-Sep GMP: 63</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4-Sep</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>8-Sep</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>3-Sep 13:01</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹150 (23.73%) 150 ↓ / 150 ↑</t>
+          <t>₹140 (22.15%) 140 ↓ / 140 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3-Sep 12:57</t>
+          <t>3-Sep 18:33</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹27 (21.77%) 23 ↓ / 27 ↑</t>
+          <t>₹30 (24.19%) 23 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,77 +608,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3-Sep 13:00</t>
+          <t>3-Sep 18:36</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Rays of Belief IPOCT</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹63 (26.36%) 10 ↓ / 63 ↑</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>36.74x</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>₹125.00 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1-Sep GMP: 38</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3-Sep GMP: 63</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>4-Sep</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>8-Sep</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>3-Sep 13:01</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kanohar Electricals IPOU</t>
+          <t>Glass Wall Systems IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹140 (22.15%) 140 ↓ / 140 ↑</t>
+          <t>₹45 (24.73%) 20 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -506,17 +506,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹1055.74 Cr</t>
+          <t>₹427.89 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3-Sep 18:33</t>
+          <t>4-Sep 13:06</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,65 +553,132 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Kanohar Electricals IPOU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹205 (32.44%) 200 ↓ / 205 ↑</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹1055.74 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>8-Sep</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4-Sep 13:12</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Pranav Constructions IPOU</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹30 (24.19%) 23 ↓ / 30 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹33 (26.61%) 23 ↓ / 33 ↑</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>124</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>₹351.03 Cr</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>7-Sep</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>9-Sep</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>10-Sep</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>15-Sep</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>3-Sep 18:36</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>4-Sep 13:12</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Glass Wall Systems IPOU</t>
+          <t>Kanohar Electricals IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹45 (24.73%) 20 ↓ / 45 ↑</t>
+          <t>₹205 (32.44%) 200 ↓ / 205 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -506,17 +506,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹427.89 Cr</t>
+          <t>₹1055.74 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4-Sep 13:06</t>
+          <t>4-Sep 18:35</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kanohar Electricals IPOU</t>
+          <t>Prasol Chemicals IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹205 (32.44%) 200 ↓ / 205 ↑</t>
+          <t>₹170 (25.15%) 14 ↓ / 170 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹1055.74 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4-Sep 13:12</t>
+          <t>4-Sep 18:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,65 +620,132 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Glass Wall Systems IPOU</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹63 (34.62%) 20 ↓ / 63 ↑</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>₹427.89 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>8-Sep</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>4-Sep 18:30</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Pranav Constructions IPOU</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹33 (26.61%) 23 ↓ / 33 ↑</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>₹34 (27.42%) 23 ↓ / 34 ↑</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>124</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>₹351.03 Cr</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>7-Sep</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>9-Sep</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>10-Sep</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>15-Sep</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>4-Sep 13:12</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>4-Sep 18:33</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kanohar Electricals IPOU</t>
+          <t>Rentomojo IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹205 (32.44%) 200 ↓ / 205 ↑</t>
+          <t>₹170 (42.08%) 79 ↓ / 170 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -506,42 +506,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹1055.74 Cr</t>
+          <t>₹1255.57 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4-Sep 18:35</t>
+          <t>5-Sep 12:28</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prasol Chemicals IPOU</t>
+          <t>Kanohar Electricals IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹170 (25.15%) 14 ↓ / 170 ↑</t>
+          <t>₹205 (32.44%) 200 ↓ / 205 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹1055.74 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4-Sep 18:37</t>
+          <t>5-Sep 12:36</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Glass Wall Systems IPOU</t>
+          <t>Prasol Chemicals IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹63 (34.62%) 20 ↓ / 63 ↑</t>
+          <t>₹165 (24.41%) 14 ↓ / 165 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -640,17 +640,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹427.89 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4-Sep 18:30</t>
+          <t>5-Sep 12:29</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,65 +687,132 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Glass Wall Systems IPOU</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>₹67 (36.81%) 20 ↓ / 67 ↑</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>₹427.89 Cr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>8-Sep</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5-Sep 12:28</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Pranav Constructions IPOU</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>₹34 (27.42%) 23 ↓ / 34 ↑</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>₹37 (29.84%) 23 ↓ / 37 ↑</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>124</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>₹351.03 Cr</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>7-Sep</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>9-Sep</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>10-Sep</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>15-Sep</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>4-Sep 18:33</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5-Sep 12:36</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹170 (42.08%) 79 ↓ / 170 ↑</t>
+          <t>₹154 (38.12%) 79 ↓ / 154 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5-Sep 12:28</t>
+          <t>5-Sep 17:57</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹205 (32.44%) 200 ↓ / 205 ↑</t>
+          <t>₹189 (29.91%) 189 ↓ / 205 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5-Sep 12:36</t>
+          <t>5-Sep 17:54</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5-Sep 12:29</t>
+          <t>5-Sep 18:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹67 (36.81%) 20 ↓ / 67 ↑</t>
+          <t>₹70 (38.46%) 20 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5-Sep 12:28</t>
+          <t>5-Sep 18:00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹37 (29.84%) 23 ↓ / 37 ↑</t>
+          <t>₹41 (33.06%) 23 ↓ / 41 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>5-Sep 12:36</t>
+          <t>5-Sep 17:59</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rentomojo IPOU</t>
+          <t>Veegaland Developers IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹154 (38.12%) 79 ↓ / 154 ↑</t>
+          <t>₹30 (21.43%) 18 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -506,42 +506,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹1255.57 Cr</t>
+          <t>₹210.00 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>9-Sep</t>
+          <t>10-Sep</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5-Sep 17:57</t>
+          <t>6-Sep 12:56</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kanohar Electricals IPOU</t>
+          <t>Rentomojo IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹189 (29.91%) 189 ↓ / 205 ↑</t>
+          <t>₹155 (38.37%) 79 ↓ / 155 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -573,42 +573,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹1055.74 Cr</t>
+          <t>₹1255.57 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5-Sep 17:54</t>
+          <t>6-Sep 13:00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Prasol Chemicals IPOU</t>
+          <t>Karamtara Engineering IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹165 (24.41%) 14 ↓ / 165 ↑</t>
+          <t>₹55 (21.65%) 40 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -640,42 +640,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹875.00 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5-Sep 18:00</t>
+          <t>6-Sep 12:56</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,12 +687,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Glass Wall Systems IPOU</t>
+          <t>Kanohar Electricals IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹70 (38.46%) 20 ↓ / 70 ↑</t>
+          <t>₹205 (32.44%) 190 ↓ / 205 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹427.89 Cr</t>
+          <t>₹1055.74 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5-Sep 18:00</t>
+          <t>6-Sep 12:54</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -754,65 +754,132 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Glass Wall Systems IPOU</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>₹44 (24.18%) 20 ↓ / 65 ↑</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>₹427.89 Cr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>8-Sep</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6-Sep 12:58</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Pranav Constructions IPOU</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>₹41 (33.06%) 23 ↓ / 41 ↑</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>₹43.5 (35.08%) 23 ↓ / 43.50 ↑</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>124</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>₹351.03 Cr</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>7-Sep</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>9-Sep</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>10-Sep</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>15-Sep</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>5-Sep 17:59</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6-Sep 12:56</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6-Sep 12:56</t>
+          <t>6-Sep 17:59</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹155 (38.37%) 79 ↓ / 155 ↑</t>
+          <t>₹137 (33.91%) 79 ↓ / 155 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6-Sep 13:00</t>
+          <t>6-Sep 17:54</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>6-Sep 12:56</t>
+          <t>6-Sep 18:01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>6-Sep 12:54</t>
+          <t>6-Sep 18:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Glass Wall Systems IPOU</t>
+          <t>Pranav Constructions IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹44 (24.18%) 20 ↓ / 65 ↑</t>
+          <t>₹43 (34.68%) 23 ↓ / 43 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -774,112 +774,45 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹427.89 Cr</t>
+          <t>₹351.03 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>9-Sep</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>10-Sep</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>11-Sep</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>6-Sep 12:58</t>
+          <t>6-Sep 17:57</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Pranav Constructions IPOU</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>₹43.5 (35.08%) 23 ↓ / 43.50 ↑</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>₹351.03 Cr</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>7-Sep</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>9-Sep</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>10-Sep</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>15-Sep</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>6-Sep 12:56</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6-Sep 17:59</t>
+          <t>7-Sep 13:31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹137 (33.91%) 79 ↓ / 155 ↑</t>
+          <t>₹142 (35.15%) 79 ↓ / 155 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6-Sep 17:54</t>
+          <t>7-Sep 13:36</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹55 (21.65%) 40 ↓ / 55 ↑</t>
+          <t>₹57 (22.44%) 40 ↓ / 57 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>6-Sep 18:01</t>
+          <t>7-Sep 13:35</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹205 (32.44%) 190 ↓ / 205 ↑</t>
+          <t>₹193 (30.54%) 190 ↓ / 205 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>6-Sep 18:02</t>
+          <t>7-Sep 13:31</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pranav Constructions IPOU</t>
+          <t>Glass Wall Systems IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹43 (34.68%) 23 ↓ / 43 ↑</t>
+          <t>₹38 (20.88%) 20 ↓ / 65 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -774,45 +774,112 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>₹427.89 Cr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>8-Sep</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>7-Sep 13:31</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Pranav Constructions IPOO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>₹43 (34.68%) 23 ↓ / 44 ↑</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3.42x</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>₹351.03 Cr</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>7-Sep</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>7-Sep GMP: 43</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>9-Sep</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>10-Sep</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>15-Sep</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>6-Sep 17:57</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>7-Sep 13:33</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Veegaland Developers IPOU</t>
+          <t>Manika Plastech IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹30 (21.43%) 18 ↓ / 30 ↑</t>
+          <t>₹20 (46.51%) 20 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -506,42 +506,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹210.00 Cr</t>
+          <t>₹125.50 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7-Sep 13:31</t>
+          <t>7-Sep 19:55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rentomojo IPOU</t>
+          <t>Veegaland Developers IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹142 (35.15%) 79 ↓ / 155 ↑</t>
+          <t>₹30 (21.43%) 18 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -573,42 +573,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹1255.57 Cr</t>
+          <t>₹210.00 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9-Sep</t>
+          <t>10-Sep</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7-Sep 13:36</t>
+          <t>7-Sep 19:59</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Karamtara Engineering IPOU</t>
+          <t>Rentomojo IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹57 (22.44%) 40 ↓ / 57 ↑</t>
+          <t>₹125 (30.94%) 79 ↓ / 155 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -640,17 +640,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹875.00 Cr</t>
+          <t>₹1255.57 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>7-Sep 13:35</t>
+          <t>7-Sep 20:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,12 +687,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kanohar Electricals IPOU</t>
+          <t>Karamtara Engineering IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹193 (30.54%) 190 ↓ / 205 ↑</t>
+          <t>₹58 (22.83%) 40 ↓ / 58 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -707,42 +707,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹1055.74 Cr</t>
+          <t>₹875.00 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>7-Sep 13:31</t>
+          <t>7-Sep 19:56</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Glass Wall Systems IPOU</t>
+          <t>Kanohar Electricals IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹38 (20.88%) 20 ↓ / 65 ↑</t>
+          <t>₹196 (31.01%) 190 ↓ / 205 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹427.89 Cr</t>
+          <t>₹1055.74 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>7-Sep 13:31</t>
+          <t>7-Sep 19:53</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -821,65 +821,132 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Glass Wall Systems IPOU</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>₹44 (24.18%) 20 ↓ / 65 ↑</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>₹427.89 Cr</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>8-Sep</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>7-Sep 19:55</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Pranav Constructions IPOO</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>₹43 (34.68%) 23 ↓ / 44 ↑</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>₹42.5 (34.27%) 23 ↓ / 44 ↑</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3.42x</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6.03x</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>124</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>₹351.03 Cr</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>7-Sep GMP: 43</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>7-Sep GMP: 42.5</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>9-Sep</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>10-Sep</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>15-Sep</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>7-Sep 13:33</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>7-Sep 19:57</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹20 (46.51%) 20 ↓ / 20 ↑</t>
+          <t>₹17 (39.53%) 17 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7-Sep 19:55</t>
+          <t>8-Sep 13:01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7-Sep 19:59</t>
+          <t>8-Sep 12:59</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rentomojo IPOU</t>
+          <t>LCC Projects IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹125 (30.94%) 79 ↓ / 155 ↑</t>
+          <t>₹30 (20.55%) 17 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -640,17 +640,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹1255.57 Cr</t>
+          <t>₹427.14 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>7-Sep 20:00</t>
+          <t>8-Sep 12:54</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹58 (22.83%) 40 ↓ / 58 ↑</t>
+          <t>₹60 (23.62%) 40 ↓ / 60 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>7-Sep 19:56</t>
+          <t>8-Sep 12:57</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kanohar Electricals IPOU</t>
+          <t>Rentomojo IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹196 (31.01%) 190 ↓ / 205 ↑</t>
+          <t>₹127 (31.44%) 79 ↓ / 155 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -774,42 +774,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹1055.74 Cr</t>
+          <t>₹1255.57 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>7-Sep 19:53</t>
+          <t>8-Sep 12:54</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -821,12 +821,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Glass Wall Systems IPOU</t>
+          <t>Kanohar Electricals IPOO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹44 (24.18%) 20 ↓ / 65 ↑</t>
+          <t>₹215 (34.02%) 190 ↓ / 215 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -836,27 +836,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.12x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹427.89 Cr</t>
+          <t>₹1055.74 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>8-Sep GMP: 215</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>7-Sep 19:55</t>
+          <t>8-Sep 13:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -888,65 +888,132 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Glass Wall Systems IPOO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>₹53 (29.12%) 20 ↓ / 65 ↑</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.02x</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>₹427.89 Cr</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>8-Sep GMP: 53</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>8-Sep 13:01</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Pranav Constructions IPOO</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>₹42.5 (34.27%) 23 ↓ / 44 ↑</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>₹44 (35.48%) 23 ↓ / 44 ↑</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>6.03x</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>124</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>₹351.03 Cr</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>7-Sep GMP: 42.5</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>9-Sep</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>10-Sep</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>15-Sep</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>7-Sep 19:57</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>8-Sep 12:55</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8-Sep 13:01</t>
+          <t>8-Sep 18:32</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8-Sep 12:59</t>
+          <t>8-Sep 18:36</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LCC Projects IPOU</t>
+          <t>Steamhouse IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹30 (20.55%) 17 ↓ / 30 ↑</t>
+          <t>₹18 (22.22%) 18 ↓ / 18 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -640,17 +640,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹427.14 Cr</t>
+          <t>₹414.00 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8-Sep 12:54</t>
+          <t>8-Sep 18:30</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,12 +687,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Karamtara Engineering IPOU</t>
+          <t>Asset Reconstruction IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹60 (23.62%) 40 ↓ / 60 ↑</t>
+          <t>₹30 (21.58%) 27 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹875.00 Cr</t>
+          <t>₹732.97 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8-Sep 12:57</t>
+          <t>8-Sep 18:35</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹127 (31.44%) 79 ↓ / 155 ↑</t>
+          <t>₹130 (32.18%) 79 ↓ / 155 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8-Sep 12:54</t>
+          <t>8-Sep 18:28</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -821,12 +821,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kanohar Electricals IPOO</t>
+          <t>Karamtara Engineering IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹215 (34.02%) 190 ↓ / 215 ↑</t>
+          <t>₹68 (26.77%) 40 ↓ / 68 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -836,47 +836,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.12x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹1055.74 Cr</t>
+          <t>₹875.00 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 215</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8-Sep 13:00</t>
+          <t>8-Sep 18:31</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹53 (29.12%) 20 ↓ / 65 ↑</t>
+          <t>₹56 (30.77%) 20 ↓ / 65 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.02x</t>
+          <t>0.75x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 53</t>
+          <t>8-Sep GMP: 56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8-Sep 13:01</t>
+          <t>8-Sep 18:32</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -955,65 +955,132 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Kanohar Electricals IPOO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>₹218 (34.49%) 190 ↓ / 218 ↑</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.73x</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>₹1055.74 Cr</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>8-Sep GMP: 218</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>8-Sep 18:37</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Pranav Constructions IPOO</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>₹44 (35.48%) 23 ↓ / 44 ↑</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>₹41 (33.06%) 23 ↓ / 44 ↑</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>6.03x</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>19.12x</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>124</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>₹351.03 Cr</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>7-Sep GMP: 42.5</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>9-Sep</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>10-Sep</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>15-Sep</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>8-Sep 12:55</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>8-Sep 18:29</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8-Sep 18:32</t>
+          <t>9-Sep 12:53</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Veegaland Developers IPOU</t>
+          <t>LCC Projects IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹30 (21.43%) 18 ↓ / 30 ↑</t>
+          <t>₹40 (27.40%) 17 ↓ / 40 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,47 +568,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.53x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹210.00 Cr</t>
+          <t>₹427.14 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>9-Sep GMP: 40</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>15-Sep</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>16-Sep</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8-Sep 18:36</t>
+          <t>9-Sep 12:56</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Steamhouse IPOU</t>
+          <t>Asset Reconstruction IPOO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹18 (22.22%) 18 ↓ / 18 ↑</t>
+          <t>₹28 (20.14%) 27 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,27 +635,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.21x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹414.00 Cr</t>
+          <t>₹732.97 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9-Sep</t>
+          <t>9-Sep GMP: 28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8-Sep 18:30</t>
+          <t>9-Sep 12:53</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,12 +687,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Asset Reconstruction IPOU</t>
+          <t>Rentomojo IPOO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹30 (21.58%) 27 ↓ / 30 ↑</t>
+          <t>₹140 (34.65%) 79 ↓ / 155 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,27 +702,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.73x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹732.97 Cr</t>
+          <t>₹1255.57 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9-Sep</t>
+          <t>9-Sep GMP: 140</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8-Sep 18:35</t>
+          <t>9-Sep 12:59</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rentomojo IPOU</t>
+          <t>Steamhouse IPOO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹130 (32.18%) 79 ↓ / 155 ↑</t>
+          <t>₹17 (20.99%) 17 ↓ / 18 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -769,27 +769,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.21x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹1255.57 Cr</t>
+          <t>₹414.00 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9-Sep</t>
+          <t>9-Sep GMP: 17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8-Sep 18:28</t>
+          <t>9-Sep 12:53</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -821,12 +821,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Karamtara Engineering IPOU</t>
+          <t>Karamtara Engineering IPOO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹68 (26.77%) 40 ↓ / 68 ↑</t>
+          <t>₹65 (25.59%) 40 ↓ / 68 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.81x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9-Sep</t>
+          <t>9-Sep GMP: 65</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8-Sep 18:31</t>
+          <t>9-Sep 12:59</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -888,12 +888,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Glass Wall Systems IPOO</t>
+          <t>Kanohar Electricals IPOO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹56 (30.77%) 20 ↓ / 65 ↑</t>
+          <t>₹225 (35.60%) 190 ↓ / 225 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -903,27 +903,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.75x</t>
+          <t>5.84x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹427.89 Cr</t>
+          <t>₹1055.74 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 56</t>
+          <t>8-Sep GMP: 218</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8-Sep 18:32</t>
+          <t>9-Sep 13:02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -955,12 +955,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kanohar Electricals IPOO</t>
+          <t>Glass Wall Systems IPOO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹218 (34.49%) 190 ↓ / 218 ↑</t>
+          <t>₹58 (31.87%) 20 ↓ / 65 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -970,27 +970,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.73x</t>
+          <t>5.6x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹1055.74 Cr</t>
+          <t>₹427.89 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 218</t>
+          <t>8-Sep GMP: 56</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8-Sep 18:37</t>
+          <t>9-Sep 12:59</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1022,12 +1022,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pranav Constructions IPOO</t>
+          <t>Pranav Constructions IPOCT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹41 (33.06%) 23 ↓ / 44 ↑</t>
+          <t>₹40.5 (32.66%) 23 ↓ / 44 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19.12x</t>
+          <t>48.5x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9-Sep</t>
+          <t>9-Sep GMP: 40.5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>8-Sep 18:29</t>
+          <t>9-Sep 12:53</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>9-Sep 12:53</t>
+          <t>9-Sep 18:56</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LCC Projects IPOO</t>
+          <t>Steamhouse IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹40 (27.40%) 17 ↓ / 40 ↑</t>
+          <t>₹20 (24.69%) 18 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,27 +568,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.53x</t>
+          <t>0.44x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹427.14 Cr</t>
+          <t>₹414.00 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 40</t>
+          <t>9-Sep GMP: 20</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>9-Sep 12:56</t>
+          <t>9-Sep 18:58</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Asset Reconstruction IPOO</t>
+          <t>LCC Projects IPOO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹28 (20.14%) 27 ↓ / 30 ↑</t>
+          <t>₹40 (27.40%) 17 ↓ / 40 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,27 +635,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.21x</t>
+          <t>1.35x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹732.97 Cr</t>
+          <t>₹427.14 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 28</t>
+          <t>9-Sep GMP: 40</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>9-Sep 12:53</t>
+          <t>9-Sep 18:59</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹140 (34.65%) 79 ↓ / 155 ↑</t>
+          <t>₹143 (35.40%) 79 ↓ / 155 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.73x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 140</t>
+          <t>9-Sep GMP: 143</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>9-Sep 12:59</t>
+          <t>9-Sep 18:53</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Steamhouse IPOO</t>
+          <t>Karamtara Engineering IPOO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹17 (20.99%) 17 ↓ / 18 ↑</t>
+          <t>₹72 (28.35%) 40 ↓ / 72 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -769,27 +769,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.21x</t>
+          <t>1.34x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹414.00 Cr</t>
+          <t>₹875.00 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 17</t>
+          <t>9-Sep GMP: 72</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>9-Sep 12:53</t>
+          <t>9-Sep 18:57</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -821,12 +821,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Karamtara Engineering IPOO</t>
+          <t>Glass Wall Systems IPOO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹65 (25.59%) 40 ↓ / 68 ↑</t>
+          <t>₹62 (34.07%) 20 ↓ / 65 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -836,47 +836,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.81x</t>
+          <t>8.23x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹875.00 Cr</t>
+          <t>₹427.89 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 65</t>
+          <t>8-Sep GMP: 56</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>11-Sep</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>15-Sep</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>9-Sep 12:59</t>
+          <t>9-Sep 18:58</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹225 (35.60%) 190 ↓ / 225 ↑</t>
+          <t>₹223 (35.28%) 190 ↓ / 223 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.84x</t>
+          <t>10.22x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -943,144 +943,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>9-Sep 13:02</t>
+          <t>9-Sep 18:55</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Glass Wall Systems IPOO</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>₹58 (31.87%) 20 ↓ / 65 ↑</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>5.6x</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>₹427.89 Cr</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>8-Sep GMP: 56</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10-Sep</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>11-Sep</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>16-Sep</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>9-Sep 12:59</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Pranav Constructions IPOCT</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>₹40.5 (32.66%) 23 ↓ / 44 ↑</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>48.5x</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>₹351.03 Cr</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>7-Sep GMP: 42.5</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>9-Sep GMP: 40.5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>10-Sep</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>15-Sep</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>9-Sep 12:53</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹17 (39.53%) 17 ↓ / 20 ↑</t>
+          <t>₹13 (30.23%) 13 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>9-Sep 18:56</t>
+          <t>10-Sep 12:57</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Steamhouse IPOO</t>
+          <t>LCC Projects IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹20 (24.69%) 18 ↓ / 20 ↑</t>
+          <t>₹49.7 (34.04%) 17 ↓ / 49.70 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,27 +568,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.44x</t>
+          <t>2.52x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹414.00 Cr</t>
+          <t>₹427.14 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>9-Sep GMP: 40</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>9-Sep 18:58</t>
+          <t>10-Sep 12:59</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LCC Projects IPOO</t>
+          <t>Karamtara Engineering IPOO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹40 (27.40%) 17 ↓ / 40 ↑</t>
+          <t>₹67 (26.38%) 40 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,27 +635,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.35x</t>
+          <t>2.43x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹427.14 Cr</t>
+          <t>₹875.00 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 40</t>
+          <t>9-Sep GMP: 75</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>9-Sep 18:59</t>
+          <t>10-Sep 13:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,12 +687,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rentomojo IPOO</t>
+          <t>Steamhouse IPOO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹143 (35.40%) 79 ↓ / 155 ↑</t>
+          <t>₹20 (24.69%) 18 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,27 +702,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>1.12x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹1255.57 Cr</t>
+          <t>₹414.00 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 143</t>
+          <t>9-Sep GMP: 20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>9-Sep 18:53</t>
+          <t>10-Sep 12:53</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Karamtara Engineering IPOO</t>
+          <t>Rentomojo IPOO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹72 (28.35%) 40 ↓ / 72 ↑</t>
+          <t>₹141 (34.90%) 79 ↓ / 155 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -769,27 +769,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.34x</t>
+          <t>3.05x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹875.00 Cr</t>
+          <t>₹1255.57 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 72</t>
+          <t>9-Sep GMP: 143</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>9-Sep 18:57</t>
+          <t>10-Sep 12:57</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -821,12 +821,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Glass Wall Systems IPOO</t>
+          <t>Kanohar Electricals IPOCT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹62 (34.07%) 20 ↓ / 65 ↑</t>
+          <t>₹225 (35.60%) 190 ↓ / 225 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -836,32 +836,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.23x</t>
+          <t>24.89x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹427.89 Cr</t>
+          <t>₹1055.74 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 56</t>
+          <t>8-Sep GMP: 218</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>10-Sep GMP: 225</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>9-Sep 18:58</t>
+          <t>10-Sep 13:01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -888,12 +888,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kanohar Electricals IPOO</t>
+          <t>Glass Wall Systems IPOCT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹223 (35.28%) 190 ↓ / 223 ↑</t>
+          <t>₹51 (28.02%) 20 ↓ / 66 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -903,32 +903,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10.22x</t>
+          <t>22.75x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹1055.74 Cr</t>
+          <t>₹427.89 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 218</t>
+          <t>8-Sep GMP: 56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>10-Sep GMP: 51</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>9-Sep 18:55</t>
+          <t>10-Sep 12:55</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10-Sep 12:57</t>
+          <t>10-Sep 18:31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52x</t>
+          <t>3.93x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10-Sep 12:59</t>
+          <t>10-Sep 18:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹67 (26.38%) 40 ↓ / 75 ↑</t>
+          <t>₹69 (27.17%) 40 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.43x</t>
+          <t>3.8x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10-Sep 13:00</t>
+          <t>10-Sep 18:32</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹20 (24.69%) 18 ↓ / 20 ↑</t>
+          <t>₹22 (27.16%) 18 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.12x</t>
+          <t>2.32x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10-Sep 12:53</t>
+          <t>10-Sep 18:32</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.05x</t>
+          <t>4.71x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -809,144 +809,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10-Sep 12:57</t>
+          <t>10-Sep 18:34</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Kanohar Electricals IPOCT</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>₹225 (35.60%) 190 ↓ / 225 ↑</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>24.89x</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>₹1055.74 Cr</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>8-Sep GMP: 218</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10-Sep GMP: 225</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>11-Sep</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>16-Sep</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>10-Sep 13:01</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Glass Wall Systems IPOCT</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>₹51 (28.02%) 20 ↓ / 66 ↑</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>22.75x</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>₹427.89 Cr</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>8-Sep GMP: 56</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10-Sep GMP: 51</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>11-Sep</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>16-Sep</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>10-Sep 12:55</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Manika Plastech IPOU</t>
+          <t>Jindal Supreme IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹13 (30.23%) 13 ↓ / 20 ↑</t>
+          <t>₹21 (22.58%) 11 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -506,42 +506,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹125.50 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10-Sep 18:31</t>
+          <t>11-Sep 12:59</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LCC Projects IPOO</t>
+          <t>Manika Plastech IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹49.7 (34.04%) 17 ↓ / 49.70 ↑</t>
+          <t>₹10 (23.26%) 10 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,47 +568,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.93x</t>
+          <t>0.88x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹427.14 Cr</t>
+          <t>₹125.50 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 40</t>
+          <t>11-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10-Sep 18:37</t>
+          <t>11-Sep 12:56</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Karamtara Engineering IPOO</t>
+          <t>Karamtara Engineering IPOCT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹69 (27.17%) 40 ↓ / 75 ↑</t>
+          <t>₹65 (25.59%) 40 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.8x</t>
+          <t>12.31x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>11-Sep GMP: 65</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10-Sep 18:32</t>
+          <t>11-Sep 12:54</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,12 +687,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Steamhouse IPOO</t>
+          <t>Rentomojo IPOCT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹22 (27.16%) 18 ↓ / 22 ↑</t>
+          <t>₹138 (34.16%) 79 ↓ / 155 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,32 +702,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.32x</t>
+          <t>14.51x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹414.00 Cr</t>
+          <t>₹1255.57 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>9-Sep GMP: 143</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>11-Sep GMP: 138</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10-Sep 18:32</t>
+          <t>11-Sep 13:00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rentomojo IPOO</t>
+          <t>Steamhouse IPOCT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹141 (34.90%) 79 ↓ / 155 ↑</t>
+          <t>₹22.75 (28.09%) 18 ↓ / 23 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -769,32 +769,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.71x</t>
+          <t>9.21x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹1255.57 Cr</t>
+          <t>₹414.00 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 143</t>
+          <t>9-Sep GMP: 20</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>11-Sep GMP: 22.75</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -809,10 +809,77 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10-Sep 18:34</t>
+          <t>11-Sep 12:54</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LCC Projects IPOCT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>₹55 (37.67%) 17 ↓ / 55 ↑</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>13.69x</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>₹427.14 Cr</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9-Sep GMP: 40</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>11-Sep GMP: 55</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>15-Sep</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>17-Sep</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>11-Sep 13:02</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>11-Sep 12:59</t>
+          <t>11-Sep 18:34</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.88x</t>
+          <t>1.49x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -608,278 +608,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>11-Sep 12:56</t>
+          <t>11-Sep 18:31</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Karamtara Engineering IPOCT</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹65 (25.59%) 40 ↓ / 75 ↑</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>12.31x</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>₹875.00 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>9-Sep GMP: 75</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>11-Sep GMP: 65</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>15-Sep</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>17-Sep</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>11-Sep 12:54</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Rentomojo IPOCT</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>₹138 (34.16%) 79 ↓ / 155 ↑</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>14.51x</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>₹1255.57 Cr</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>9-Sep GMP: 143</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>11-Sep GMP: 138</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>15-Sep</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>17-Sep</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>11-Sep 13:00</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Steamhouse IPOCT</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>₹22.75 (28.09%) 18 ↓ / 23 ↑</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>9.21x</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>₹414.00 Cr</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>9-Sep GMP: 20</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>11-Sep GMP: 22.75</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>15-Sep</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>17-Sep</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>11-Sep 12:54</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LCC Projects IPOCT</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>₹55 (37.67%) 17 ↓ / 55 ↑</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>13.69x</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>₹427.14 Cr</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>9-Sep GMP: 40</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>11-Sep GMP: 55</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>15-Sep</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>17-Sep</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>11-Sep 13:02</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOU</t>
+          <t>SS Retail IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹21 (22.58%) 11 ↓ / 21 ↑</t>
+          <t>₹110 (25.94%) 30 ↓ / 110 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -506,17 +506,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹124.88 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>11-Sep 18:34</t>
+          <t>12-Sep 12:55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Manika Plastech IPOO</t>
+          <t>Jindal Supreme IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹10 (23.26%) 10 ↓ / 20 ↑</t>
+          <t>₹21 (22.58%) 11 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,50 +568,117 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.49x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹125.50 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 10</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>18-Sep</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>21-Sep</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>23-Sep</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>12-Sep 12:55</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Hero Motors IPOU</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹24 (28.57%) 8 ↓ / 24 ↑</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>₹1000.00 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>16-Sep</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>17-Sep</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>18-Sep</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>21-Sep</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>11-Sep 18:31</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>23-Sep</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>12-Sep 12:59</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹110 (25.94%) 30 ↓ / 110 ↑</t>
+          <t>₹106 (25.00%) 30 ↓ / 106 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>12-Sep 12:55</t>
+          <t>12-Sep 18:01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOU</t>
+          <t>Hero Motors IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹21 (22.58%) 11 ↓ / 21 ↑</t>
+          <t>₹24 (28.57%) 8 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹124.88 Cr</t>
+          <t>₹1000.00 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12-Sep 12:55</t>
+          <t>12-Sep 17:57</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hero Motors IPOU</t>
+          <t>Jindal Supreme IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹24 (28.57%) 8 ↓ / 24 ↑</t>
+          <t>₹21 (22.58%) 11 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -640,17 +640,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹1000.00 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -675,10 +675,77 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12-Sep 12:59</t>
+          <t>12-Sep 17:55</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Manika Plastech IPOO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>₹15 (34.88%) 7 ↓ / 20 ↑</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.49x</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>₹125.50 Cr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>11-Sep GMP: 7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>17-Sep</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>21-Sep</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>12-Sep 17:57</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹106 (25.00%) 30 ↓ / 106 ↑</t>
+          <t>₹99 (23.35%) 30 ↓ / 106 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>12-Sep 18:01</t>
+          <t>13-Sep 13:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12-Sep 17:57</t>
+          <t>13-Sep 13:30</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹21 (22.58%) 11 ↓ / 21 ↑</t>
+          <t>₹25 (26.88%) 11 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12-Sep 17:55</t>
+          <t>13-Sep 13:32</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹15 (34.88%) 7 ↓ / 20 ↑</t>
+          <t>₹11 (25.58%) 7 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>12-Sep 17:57</t>
+          <t>13-Sep 13:32</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
